--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="15" max="15" width="20.7109375" style="2" customWidth="1"/>
@@ -1394,46 +1394,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rincón de Aranda (RDA)</t>
+          <t>Sal de Oro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pampa Energía (Argentina)</t>
+          <t>Posco (Corea del Sur)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sucursal Dedicada Midstream RDA</t>
+          <t>Argentina S.A. (Posco)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>NOA</t>
         </is>
       </c>
       <c r="K18">
-        <v>4500</v>
+        <v>845</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="O18" s="2">
-        <v>45839</v>
+        <v>45595</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -1452,22 +1452,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sal de Oro</t>
+          <t>Sal de Vida</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Posco (Corea del Sur)</t>
+          <t>Rio Tinto (Reino Unido)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Argentina S.A. (Posco)</t>
+          <t>Sal de Vida S.A.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="K19">
-        <v>845</v>
+        <v>818</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="O19" s="2">
-        <v>45595</v>
+        <v>45758</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -1510,22 +1510,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sal de Vida</t>
+          <t>Salterra</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rio Tinto (Reino Unido)</t>
+          <t>Zijin Mining (LieX S.A.) (China)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sal de Vida S.A.</t>
+          <t>LIEX S.A.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1549,15 +1549,12 @@
         </is>
       </c>
       <c r="K20">
-        <v>818</v>
+        <v>710</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
-      </c>
-      <c r="O20" s="2">
-        <v>45758</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -1568,22 +1565,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Salterra</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Zijin Mining (LieX S.A.) (China)</t>
+          <t>BHP (Australia); Lundin Mining (Canadá)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LIEX S.A.</t>
+          <t>Vicuña Argentina S.A.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1593,86 +1590,31 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>NOA</t>
+          <t>Cuyo</t>
         </is>
       </c>
       <c r="K21">
-        <v>710</v>
+        <v>9712</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
+      <c r="O21" s="2">
+        <v>46002</v>
+      </c>
       <c r="U21" t="inlineStr">
-        <is>
-          <t>Globaris</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Vicuña</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>BHP (Australia); Lundin Mining (Canadá)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Vicuña Argentina S.A.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Minería</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Cobre</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>San Juan</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Cuyo</t>
-        </is>
-      </c>
-      <c r="K22">
-        <v>9712</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O22" s="2">
-        <v>46002</v>
-      </c>
-      <c r="U22" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -355,13 +355,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="15" max="15" width="20.7109375" style="2" customWidth="1"/>
     <col min="16" max="16" width="20.7109375" style="2" customWidth="1"/>
     <col min="17" max="17" width="20.7109375" style="2" customWidth="1"/>
     <col min="18" max="18" width="20.7109375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -382,100 +382,105 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Proyectos de exportación estratégica de largo plazo (PEELP)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>empresa</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>titular_proyecto</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>CUIT</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>subsector</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>localidad_region</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Monto (mill. USD)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Activos Computables (mill. USD)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Empleos (directos e indirectos)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Estado administrativo</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>fecha_presentacion</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>fecha_adhesion_rigi</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>fecha_publicacion_bo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>fecha_aprobacion</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>norma_aprobacion</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>link_norma</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Fuentes</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Clasificación preexistencia BO</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Justificación preexistencia BO</t>
         </is>
@@ -492,48 +497,48 @@
           <t>Ángeles Argentina</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Xizang Zhufeng Resources Co Ltd (Tibet Summit) (China)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Potasio y Litio de Argentina SA</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Litio</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Salta</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>726</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O2" s="2">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P2" s="2">
         <v>45671</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -550,48 +555,48 @@
           <t>Arenas de Cercanía</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Minera del Mojotoro (Argentina); Minera Orosmayo (Argentina)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Arenas de Cercanía S.A.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Arena</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Rio Negro</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Patagonia</t>
         </is>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>232</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O3" s="2">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P3" s="2">
         <v>45874</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -608,48 +613,48 @@
           <t>Bajo del Choique–La Invernada</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Pluspetrol (Argentina); Gas y Petróleo del Neuquén S.A (Argentina)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Pluspetrol Cuenca Neuquina S.R.L</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Energía</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Oil &amp; Gas</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Neuquén</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Patagonia</t>
         </is>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>12000</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O4" s="2">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P4" s="2">
         <v>45771</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -666,48 +671,48 @@
           <t>Duplicar Norte</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Oldelval (Argentina)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Oleoductos del Valle SDE</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Energía</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Oil &amp; Gas</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Neuquén</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Patagonia</t>
         </is>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>380</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O5" s="2">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P5" s="2">
         <v>45859</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -724,48 +729,48 @@
           <t>El Pachón</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Glencore (Suiza)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Glencore Pachón S.A.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Cobre</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Cuyo</t>
         </is>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>9500</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O6" s="2">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P6" s="2">
         <v>45887</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -782,43 +787,43 @@
           <t>El Trapial</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Chevron (Estados Unidos)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Energía</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Oil &amp; Gas</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Neuquén</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Patagonia</t>
         </is>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>13800</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O7" s="2">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P7" s="2">
         <v>46175</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -835,48 +840,48 @@
           <t>Fértil Pampa</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Pampa Energía (Argentina)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Fértil Pampa S.A.U.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Energía</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Oil &amp; Gas</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Buenos Aires</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Centro</t>
         </is>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>2400</v>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O8" s="2">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P8" s="2">
         <v>46136</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -893,48 +898,48 @@
           <t>Jama Solaroz</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>CNGR (China)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>CNGR Advanced Material</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Litio</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Jujuy</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>1151</v>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O9" s="2">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P9" s="2">
         <v>46111</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -951,43 +956,43 @@
           <t>LL Oil</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>YPF S.A. (Argentina)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Energía</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Oil &amp; Gas</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Neuquén</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Patagonia</t>
         </is>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>25000</v>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O10" s="2">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P10" s="2">
         <v>46157</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -1004,43 +1009,43 @@
           <t>Loma Jarillosa Este y Puesto Silva Oeste</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>GeoPark (Colombia); Gas y Petróleo del Neuquén S.A (Argentina)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Energía</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Oil &amp; Gas</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Neuquén</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Patagonia</t>
         </is>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>1000</v>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O11" s="2">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P11" s="2">
         <v>46157</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -1057,48 +1062,48 @@
           <t>Mega</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>YPF S.A. (Argentina); Petrobras (Brazil); Dow (Argentina)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Mega</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Energía</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Oil &amp; Gas</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Neuquén</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Patagonia</t>
         </is>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>360</v>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O12" s="2">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P12" s="2">
         <v>46099</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -1115,48 +1120,48 @@
           <t>Minera Agua Rica (MARA)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Glencore (Suiza)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Minera Agua Rica LLC Sucursal Argentina</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Cobre</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Catamarca</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>4000</v>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O13" s="2">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P13" s="2">
         <v>45887</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -1173,45 +1178,45 @@
           <t>NCA+ (Nuevo Central Argentino)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Nuevo Central Argentino (Argentina)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Nuevo Central Argentino</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Ferroviario</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Múltiples (Buenos Aires, Santa Fe, Santiago del Estero, Chaco)</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Centro</t>
         </is>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>200</v>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -1228,48 +1233,48 @@
           <t>Parque Eólico La Rinconada</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Tenaris (Argentina)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Vientos La Rinconada S.A.U.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Energía</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Eólico</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Buenos Aires</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Centro</t>
         </is>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>206</v>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O15" s="2">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P15" s="2">
         <v>45805</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -1286,48 +1291,48 @@
           <t>Planta de Tratamiento Los Toldos</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Tecpetrol S.A. (Argentina); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Tecpetrol S.A – Gas y Petróleo del Neuquén S.A. (UT)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Energía</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Oil &amp; Gas</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Neuquén</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Patagonia</t>
         </is>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>6391</v>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O16" s="2">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P16" s="2">
         <v>46118</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -1344,48 +1349,48 @@
           <t>Pozuelos Pastos Grandes (PPG)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Ganfeng (China); Lithium Argentina (Suiza)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Lithea Inc.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Litio</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Salta</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>4245</v>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O17" s="2">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P17" s="2">
         <v>46081</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -1402,48 +1407,48 @@
           <t>Sal de Oro</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Posco (Corea del Sur)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Argentina S.A. (Posco)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Litio</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Salta</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>845</v>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O18" s="2">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P18" s="2">
         <v>45595</v>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -1460,48 +1465,48 @@
           <t>Sal de Vida</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Rio Tinto (Reino Unido)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Sal de Vida S.A.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Litio</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Catamarca</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>818</v>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O19" s="2">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P19" s="2">
         <v>45758</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -1518,45 +1523,45 @@
           <t>Salterra</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Zijin Mining (LieX S.A.) (China)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>LIEX S.A.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Litio</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Catamarca</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>710</v>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
@@ -1573,48 +1578,48 @@
           <t>Vicuña</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>BHP (Australia); Lundin Mining (Canadá)</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Vicuña Argentina S.A.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Minería</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Cobre</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Cuyo</t>
         </is>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>9712</v>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="O21" s="2">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>En evaluación</t>
+        </is>
+      </c>
+      <c r="P21" s="2">
         <v>46002</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="16" max="16" width="20.7109375" style="2" customWidth="1"/>
@@ -1512,119 +1512,6 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Salterra</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Zijin Mining (LieX S.A.) (China)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>LIEX S.A.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Minería</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Litio</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Catamarca</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>NOA</t>
-        </is>
-      </c>
-      <c r="L20">
-        <v>710</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Globaris</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Vicuña</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>BHP (Australia); Lundin Mining (Canadá)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Vicuña Argentina S.A.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Minería</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Cobre</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>San Juan</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Cuyo</t>
-        </is>
-      </c>
-      <c r="L21">
-        <v>9712</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="P21" s="2">
-        <v>46002</v>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Globaris</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/downloads/base_interactiva_pendientes.xlsx
+++ b/downloads/base_interactiva_pendientes.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="16" max="16" width="20.7109375" style="2" customWidth="1"/>
@@ -1399,22 +1399,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sal de Oro</t>
+          <t>Sal de Vida</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Posco (Corea del Sur)</t>
+          <t>Rio Tinto (Reino Unido)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Argentina S.A. (Posco)</t>
+          <t>Sal de Vida S.A.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="L18">
-        <v>845</v>
+        <v>818</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1446,67 +1446,9 @@
         </is>
       </c>
       <c r="P18" s="2">
-        <v>45595</v>
+        <v>45758</v>
       </c>
       <c r="V18" t="inlineStr">
-        <is>
-          <t>Globaris</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Sal de Vida</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Rio Tinto (Reino Unido)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Sal de Vida S.A.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Minería</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Litio</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Catamarca</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>NOA</t>
-        </is>
-      </c>
-      <c r="L19">
-        <v>818</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>En evaluación</t>
-        </is>
-      </c>
-      <c r="P19" s="2">
-        <v>45758</v>
-      </c>
-      <c r="V19" t="inlineStr">
         <is>
           <t>Globaris</t>
         </is>
